--- a/Смета/Смета.xlsx
+++ b/Смета/Смета.xlsx
@@ -1,26 +1,103 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="122211" fullCalcOnLoad="1"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+  <si>
+    <t>№</t>
+  </si>
+  <si>
+    <t>Наименование</t>
+  </si>
+  <si>
+    <t>Магазин</t>
+  </si>
+  <si>
+    <t>Количество, шт</t>
+  </si>
+  <si>
+    <t>Цена, руб</t>
+  </si>
+  <si>
+    <t>Стоимость, руб</t>
+  </si>
+  <si>
+    <t>ozon</t>
+  </si>
+  <si>
+    <t>aliexpress</t>
+  </si>
+  <si>
+    <t>Переходник SMA-female
+ - MMCX угловой пигтейл длина 10 см</t>
+  </si>
+  <si>
+    <t>FPV камера для квадрокоптера 
+CADDXFPV Ratel Pro 1500TVL</t>
+  </si>
+  <si>
+    <t>Специальный мешок для зарядки и хранения 
+LiPol аккумуляторов Deep RC 23x30 см</t>
+  </si>
+  <si>
+    <t>Разъем прямой 
+MMCX TO SMA Female</t>
+  </si>
+  <si>
+    <t>Переключаемый VTX модуль видеопередатчика с OSD 
+для FPV дрона, JHEMCU VTX30-800 
+VTX5848 LITE 40CH 5,8G 25/100/200/400 МВт</t>
+  </si>
+  <si>
+    <t>Антенна Foxeer Pagoda Pro 5,8 GHz RHCP 86 mm 
+SMA для FPV дронов квадрокоптеров самолетов</t>
+  </si>
+  <si>
+    <t>Складной пропеллер 1180 11 x 8 дюймов 
+Haoye для авиамоделей из пластика</t>
+  </si>
+  <si>
+    <t>Замок-защелка с пружиной W-528 
+(10 шт в наборе) Никель , замок накидной</t>
+  </si>
+  <si>
+    <t>Мотор SunnySky X2814 900kv</t>
+  </si>
+  <si>
+    <t>Регулятор оборотов бесколекторного
+двигателя HobbyWing 60A</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -43,24 +120,51 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -98,7 +202,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -170,7 +274,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -343,27 +447,309 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="49.109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="5">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6">
+        <v>383.03</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="4">
+        <f>C2*D2</f>
+        <v>383.03</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4">
+        <v>5847</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="4">
+        <f>C3*D3</f>
+        <v>5847</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
+        <v>615</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="4">
+        <f t="shared" ref="F4:F11" si="0">C4*D4</f>
+        <v>615</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6">
+        <v>426</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="4">
+        <f t="shared" si="0"/>
+        <v>426</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6">
+        <v>4296.04</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="4">
+        <f t="shared" si="0"/>
+        <v>4296.04</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1288</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="4">
+        <f t="shared" si="0"/>
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1476</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="4">
+        <f t="shared" si="0"/>
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6">
+        <v>556</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="4">
+        <f t="shared" si="0"/>
+        <v>556</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6">
+        <v>3500</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6">
+        <v>2409</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="4">
+        <f t="shared" si="0"/>
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E10" r:id="rId1"/>
+    <hyperlink ref="E11" r:id="rId2"/>
+    <hyperlink ref="E2" r:id="rId3"/>
+    <hyperlink ref="E3" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E5" r:id="rId7"/>
+    <hyperlink ref="E4" r:id="rId8"/>
+    <hyperlink ref="E8" r:id="rId9"/>
+    <hyperlink ref="E9" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Смета/Смета.xlsx
+++ b/Смета/Смета.xlsx
@@ -1,22 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4392FD45-106E-40F1-B50E-D3F5D0F5E2AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
   <si>
     <t>№</t>
   </si>
@@ -80,12 +92,15 @@
   <si>
     <t>Регулятор оборотов бесколекторного
 двигателя HobbyWing 60A</t>
+  </si>
+  <si>
+    <t>OpenMV Cam H7 Plus</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -157,14 +172,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -202,7 +220,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -274,7 +292,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -447,7 +465,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -538,7 +556,7 @@
         <v>6</v>
       </c>
       <c r="F4" s="4">
-        <f t="shared" ref="F4:F11" si="0">C4*D4</f>
+        <f t="shared" ref="F4:F12" si="0">C4*D4</f>
         <v>615</v>
       </c>
     </row>
@@ -563,7 +581,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -693,11 +711,22 @@
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="B12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6">
+        <v>7040</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="4">
+        <f t="shared" si="0"/>
+        <v>7040</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
@@ -721,24 +750,25 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E10" r:id="rId1"/>
-    <hyperlink ref="E11" r:id="rId2"/>
-    <hyperlink ref="E2" r:id="rId3"/>
-    <hyperlink ref="E3" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E5" r:id="rId7"/>
-    <hyperlink ref="E4" r:id="rId8"/>
-    <hyperlink ref="E8" r:id="rId9"/>
-    <hyperlink ref="E9" r:id="rId10"/>
+    <hyperlink ref="E10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="E5" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="E4" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="E8" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="E9" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="E12" r:id="rId11" xr:uid="{92200FC3-A8B8-46FE-9040-E8EE32C18E2D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -747,7 +777,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
